--- a/results/ref_threshold_sensitivity/tables/SumRel_threshold_metrics.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_threshold_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,25 +486,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5755852889762156</v>
+        <v>0.5755852889762161</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1511705779524313</v>
+        <v>0.1511705779524322</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356185999273622</v>
+        <v>1.356185999273623</v>
       </c>
       <c r="G2" t="n">
         <v>0.199</v>
       </c>
       <c r="H2" t="n">
-        <v>190.693409899824</v>
+        <v>190.6934098998242</v>
       </c>
       <c r="I2" t="n">
         <v>331.3034810861955</v>
       </c>
       <c r="J2" t="n">
-        <v>8.294327430324548</v>
+        <v>8.294327430324556</v>
       </c>
     </row>
     <row r="3">
@@ -518,10 +518,10 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5256219687263332</v>
+        <v>0.5256219687263333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2884329530894998</v>
+        <v>0.2884329530894999</v>
       </c>
       <c r="F3" t="n">
         <v>2.216046840597066</v>
@@ -550,25 +550,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4240549598658212</v>
+        <v>0.4240549598658218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.218360302675043</v>
+        <v>0.2183603026750438</v>
       </c>
       <c r="F4" t="n">
-        <v>2.061574985258455</v>
+        <v>2.061574985258458</v>
       </c>
       <c r="G4" t="n">
         <v>0.004</v>
       </c>
       <c r="H4" t="n">
-        <v>262.0799181803195</v>
+        <v>262.0799181803198</v>
       </c>
       <c r="I4" t="n">
         <v>618.0329037142883</v>
       </c>
       <c r="J4" t="n">
-        <v>8.532316708043737</v>
+        <v>8.532316708043751</v>
       </c>
     </row>
     <row r="5">
@@ -582,10 +582,10 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3430968682153295</v>
+        <v>0.3430968682153296</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1702276230088373</v>
+        <v>0.1702276230088375</v>
       </c>
       <c r="F5" t="n">
         <v>1.98471895799337</v>
@@ -594,13 +594,13 @@
         <v>0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>248.3873571825596</v>
+        <v>248.3873571825597</v>
       </c>
       <c r="I5" t="n">
         <v>723.9569351786397</v>
       </c>
       <c r="J5" t="n">
-        <v>6.183664494146679</v>
+        <v>6.183664494146682</v>
       </c>
     </row>
     <row r="6">
@@ -614,25 +614,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3405615461937536</v>
+        <v>0.3405615461937538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2031785349841191</v>
+        <v>0.2031785349841192</v>
       </c>
       <c r="F6" t="n">
-        <v>2.478920378838444</v>
+        <v>2.478920378838445</v>
       </c>
       <c r="G6" t="n">
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>311.3986155603584</v>
+        <v>311.3986155603586</v>
       </c>
       <c r="I6" t="n">
         <v>914.3681047982918</v>
       </c>
       <c r="J6" t="n">
-        <v>7.388694435646968</v>
+        <v>7.388694435646975</v>
       </c>
     </row>
     <row r="7">
@@ -646,25 +646,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2817620862995143</v>
+        <v>0.2817620862995145</v>
       </c>
       <c r="E7" t="n">
-        <v>0.153505315995856</v>
+        <v>0.1535053159958564</v>
       </c>
       <c r="F7" t="n">
-        <v>2.196859359801592</v>
+        <v>2.196859359801594</v>
       </c>
       <c r="G7" t="n">
         <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>290.341761622797</v>
+        <v>290.3417616227973</v>
       </c>
       <c r="I7" t="n">
         <v>1030.450070255948</v>
       </c>
       <c r="J7" t="n">
-        <v>5.828707214872588</v>
+        <v>5.828707214872598</v>
       </c>
     </row>
     <row r="8">
@@ -678,25 +678,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2551292489076616</v>
+        <v>0.2551292489076619</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1422700441967012</v>
+        <v>0.1422700441967016</v>
       </c>
       <c r="F8" t="n">
-        <v>2.260597614178338</v>
+        <v>2.260597614178341</v>
       </c>
       <c r="G8" t="n">
         <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>296.5920555245091</v>
+        <v>296.5920555245094</v>
       </c>
       <c r="I8" t="n">
         <v>1162.51686858473</v>
       </c>
       <c r="J8" t="n">
-        <v>5.705509415246405</v>
+        <v>5.705509415246414</v>
       </c>
     </row>
     <row r="9">
@@ -710,25 +710,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2600434908304278</v>
+        <v>0.2600434908304277</v>
       </c>
       <c r="E9" t="n">
-        <v>0.162680792255484</v>
+        <v>0.1626807922554839</v>
       </c>
       <c r="F9" t="n">
-        <v>2.670873903831482</v>
+        <v>2.670873903831481</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>340.597427048197</v>
+        <v>340.5974270481969</v>
       </c>
       <c r="I9" t="n">
         <v>1309.77101545794</v>
       </c>
       <c r="J9" t="n">
-        <v>6.079869406982931</v>
+        <v>6.079869406982926</v>
       </c>
     </row>
     <row r="10">
@@ -742,25 +742,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2958595079622765</v>
+        <v>0.2958595079622763</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2120332589101666</v>
+        <v>0.2120332589101663</v>
       </c>
       <c r="F10" t="n">
-        <v>3.529437512805299</v>
+        <v>3.529437512805296</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>436.2145161079195</v>
+        <v>436.2145161079192</v>
       </c>
       <c r="I10" t="n">
         <v>1474.397490593876</v>
       </c>
       <c r="J10" t="n">
-        <v>7.515089085891463</v>
+        <v>7.515089085891455</v>
       </c>
     </row>
     <row r="11">
@@ -774,25 +774,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2860611958570174</v>
+        <v>0.286061195857017</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2101102592460617</v>
+        <v>0.2101102592460613</v>
       </c>
       <c r="F11" t="n">
-        <v>3.766394578151316</v>
+        <v>3.766394578151311</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>448.2318414853752</v>
+        <v>448.2318414853746</v>
       </c>
       <c r="I11" t="n">
         <v>1566.908927100395</v>
       </c>
       <c r="J11" t="n">
-        <v>7.188244463959993</v>
+        <v>7.188244463959986</v>
       </c>
     </row>
     <row r="12">
@@ -806,25 +806,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2893160670625267</v>
+        <v>0.2893160670625263</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2209810735108466</v>
+        <v>0.2209810735108461</v>
       </c>
       <c r="F12" t="n">
-        <v>4.233790800663849</v>
+        <v>4.233790800663843</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>498.1335897537959</v>
+        <v>498.1335897537953</v>
       </c>
       <c r="I12" t="n">
         <v>1721.762620415201</v>
       </c>
       <c r="J12" t="n">
-        <v>7.394514241080932</v>
+        <v>7.394514241080915</v>
       </c>
     </row>
     <row r="13">
@@ -838,25 +838,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2794460989117293</v>
+        <v>0.2794460989117291</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2151109291717053</v>
+        <v>0.215110929171705</v>
       </c>
       <c r="F13" t="n">
-        <v>4.343597755954634</v>
+        <v>4.343597755954629</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>506.8889733138345</v>
+        <v>506.888973313834</v>
       </c>
       <c r="I13" t="n">
         <v>1813.906063773498</v>
       </c>
       <c r="J13" t="n">
-        <v>7.070405377868608</v>
+        <v>7.070405377868595</v>
       </c>
     </row>
     <row r="14">
@@ -876,19 +876,19 @@
         <v>0.2060632065976186</v>
       </c>
       <c r="F14" t="n">
-        <v>4.426008656724396</v>
+        <v>4.426008656724394</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>520.0013463685009</v>
+        <v>520.0013463685008</v>
       </c>
       <c r="I14" t="n">
         <v>1953.350649935113</v>
       </c>
       <c r="J14" t="n">
-        <v>6.638738296098122</v>
+        <v>6.638738296098114</v>
       </c>
     </row>
     <row r="15">
@@ -902,25 +902,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2346826155705923</v>
+        <v>0.2346826155705918</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1767040258410918</v>
+        <v>0.1767040258410912</v>
       </c>
       <c r="F15" t="n">
-        <v>4.047746188127467</v>
+        <v>4.047746188127459</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>486.4548087603548</v>
+        <v>486.4548087603538</v>
       </c>
       <c r="I15" t="n">
         <v>2072.819955485922</v>
       </c>
       <c r="J15" t="n">
-        <v>5.8398299769993</v>
+        <v>5.839829976999286</v>
       </c>
     </row>
     <row r="16">
@@ -934,25 +934,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2323611456709237</v>
+        <v>0.2323611456709234</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1775297989331326</v>
+        <v>0.1775297989331323</v>
       </c>
       <c r="F16" t="n">
-        <v>4.237742814928424</v>
+        <v>4.237742814928419</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>496.2224308025022</v>
+        <v>496.2224308025017</v>
       </c>
       <c r="I16" t="n">
         <v>2135.565433582714</v>
       </c>
       <c r="J16" t="n">
-        <v>5.669571852455076</v>
+        <v>5.669571852455072</v>
       </c>
     </row>
     <row r="17">
@@ -966,25 +966,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2324913222434052</v>
+        <v>0.2324913222434055</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1813240770596322</v>
+        <v>0.1813240770596326</v>
       </c>
       <c r="F17" t="n">
-        <v>4.543752969470725</v>
+        <v>4.543752969470733</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>525.9191440067963</v>
+        <v>525.9191440067971</v>
       </c>
       <c r="I17" t="n">
         <v>2262.102253675468</v>
       </c>
       <c r="J17" t="n">
-        <v>5.725451480651313</v>
+        <v>5.725451480651319</v>
       </c>
     </row>
     <row r="18">
@@ -998,25 +998,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2329768550408525</v>
+        <v>0.2329768550408528</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1850379084809057</v>
+        <v>0.1850379084809062</v>
       </c>
       <c r="F18" t="n">
-        <v>4.859865970344581</v>
+        <v>4.859865970344588</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>545.9729369709576</v>
+        <v>545.9729369709584</v>
       </c>
       <c r="I18" t="n">
         <v>2343.464276205554</v>
       </c>
       <c r="J18" t="n">
-        <v>5.564041607145965</v>
+        <v>5.564041607145979</v>
       </c>
     </row>
     <row r="19">
@@ -1030,25 +1030,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2224747594224214</v>
+        <v>0.2224747594224215</v>
       </c>
       <c r="E19" t="n">
         <v>0.1761934951023275</v>
       </c>
       <c r="F19" t="n">
-        <v>4.807015596715871</v>
+        <v>4.807015596715873</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>550.5707756198966</v>
+        <v>550.5707756198968</v>
       </c>
       <c r="I19" t="n">
         <v>2474.756134355478</v>
       </c>
       <c r="J19" t="n">
-        <v>5.246150758657549</v>
+        <v>5.24615075865755</v>
       </c>
     </row>
     <row r="20">
@@ -1062,25 +1062,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2279835395489325</v>
+        <v>0.2279835395489326</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1846118282876366</v>
+        <v>0.1846118282876367</v>
       </c>
       <c r="F20" t="n">
-        <v>5.256503211861519</v>
+        <v>5.256503211861522</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>591.9513970181736</v>
+        <v>591.9513970181738</v>
       </c>
       <c r="I20" t="n">
         <v>2596.465508822938</v>
       </c>
       <c r="J20" t="n">
-        <v>5.353943655071094</v>
+        <v>5.353943655071093</v>
       </c>
     </row>
     <row r="21">
@@ -1094,25 +1094,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2141315808957042</v>
+        <v>0.2141315808957047</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1723300692412204</v>
+        <v>0.172330069241221</v>
       </c>
       <c r="F21" t="n">
-        <v>5.122579840309089</v>
+        <v>5.1225798403091</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>584.9491316892035</v>
+        <v>584.9491316892047</v>
       </c>
       <c r="I21" t="n">
         <v>2731.727516522241</v>
       </c>
       <c r="J21" t="n">
-        <v>4.985494666598608</v>
+        <v>4.985494666598618</v>
       </c>
     </row>
     <row r="22">
@@ -1126,25 +1126,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2232963412792216</v>
+        <v>0.2232963412792219</v>
       </c>
       <c r="E22" t="n">
-        <v>0.183668603589386</v>
+        <v>0.1836686035893864</v>
       </c>
       <c r="F22" t="n">
-        <v>5.634849585079805</v>
+        <v>5.634849585079812</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>635.6780566370652</v>
+        <v>635.678056637066</v>
       </c>
       <c r="I22" t="n">
         <v>2846.791187868947</v>
       </c>
       <c r="J22" t="n">
-        <v>5.342279290739271</v>
+        <v>5.342279290739274</v>
       </c>
     </row>
     <row r="23">
@@ -1158,25 +1158,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2185174809382152</v>
+        <v>0.2185174809382151</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1805814363235655</v>
+        <v>0.1805814363235654</v>
       </c>
       <c r="F23" t="n">
-        <v>5.760154574834887</v>
+        <v>5.760154574834885</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>655.3893111570945</v>
+        <v>655.3893111570943</v>
       </c>
       <c r="I23" t="n">
         <v>2999.253461751203</v>
       </c>
       <c r="J23" t="n">
-        <v>5.29944841339681</v>
+        <v>5.299448413396805</v>
       </c>
     </row>
     <row r="24">
@@ -1190,25 +1190,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2208582366458276</v>
+        <v>0.220858236645828</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1847868587127641</v>
+        <v>0.1847868587127646</v>
       </c>
       <c r="F24" t="n">
-        <v>6.122811195504285</v>
+        <v>6.122811195504295</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>705.6293275768192</v>
+        <v>705.6293275768203</v>
       </c>
       <c r="I24" t="n">
         <v>3194.942322700781</v>
       </c>
       <c r="J24" t="n">
-        <v>5.398015944144059</v>
+        <v>5.398015944144066</v>
       </c>
     </row>
     <row r="25">
@@ -1222,25 +1222,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2061241458806004</v>
+        <v>0.2061241458806003</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1706832595359844</v>
+        <v>0.1706832595359842</v>
       </c>
       <c r="F25" t="n">
-        <v>5.815998614603314</v>
+        <v>5.815998614603307</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>678.8132858778263</v>
+        <v>678.8132858778257</v>
       </c>
       <c r="I25" t="n">
         <v>3293.225463605006</v>
       </c>
       <c r="J25" t="n">
-        <v>4.960461723362691</v>
+        <v>4.960461723362688</v>
       </c>
     </row>
     <row r="26">
@@ -1272,7 +1272,7 @@
         <v>3396.016992345067</v>
       </c>
       <c r="J26" t="n">
-        <v>4.853376658121172</v>
+        <v>4.853376658121173</v>
       </c>
     </row>
     <row r="27">
@@ -1286,25 +1286,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1918685918658002</v>
+        <v>0.1918685918658001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1587484521881691</v>
+        <v>0.158748452188169</v>
       </c>
       <c r="F27" t="n">
-        <v>5.793109380978409</v>
+        <v>5.793109380978406</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>676.0836276193374</v>
+        <v>676.0836276193372</v>
       </c>
       <c r="I27" t="n">
         <v>3523.680562018274</v>
       </c>
       <c r="J27" t="n">
-        <v>4.492789531176011</v>
+        <v>4.492789531176012</v>
       </c>
     </row>
     <row r="28">
@@ -1318,25 +1318,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1912461827455566</v>
+        <v>0.1912461827455567</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1591527772989516</v>
+        <v>0.1591527772989517</v>
       </c>
       <c r="F28" t="n">
-        <v>5.959049221614721</v>
+        <v>5.959049221614723</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>697.0485726523988</v>
+        <v>697.0485726523991</v>
       </c>
       <c r="I28" t="n">
         <v>3644.77116690892</v>
       </c>
       <c r="J28" t="n">
-        <v>4.512053297405028</v>
+        <v>4.51205329740503</v>
       </c>
     </row>
     <row r="29">
@@ -1350,25 +1350,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1837642497820642</v>
+        <v>0.1837642497820643</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1526102135142041</v>
+        <v>0.1526102135142043</v>
       </c>
       <c r="F29" t="n">
-        <v>5.898569552980951</v>
+        <v>5.898569552980956</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>692.1452534146133</v>
+        <v>692.1452534146139</v>
       </c>
       <c r="I29" t="n">
         <v>3766.484799058931</v>
       </c>
       <c r="J29" t="n">
-        <v>4.283247081278815</v>
+        <v>4.283247081278818</v>
       </c>
     </row>
     <row r="30">
@@ -1382,25 +1382,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1788636025916063</v>
+        <v>0.1788636025916064</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1486747644515918</v>
+        <v>0.1486747644515919</v>
       </c>
       <c r="F30" t="n">
-        <v>5.924825651190845</v>
+        <v>5.924825651190848</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>690.698206216877</v>
+        <v>690.6982062168773</v>
       </c>
       <c r="I30" t="n">
         <v>3861.591716867779</v>
       </c>
       <c r="J30" t="n">
-        <v>4.088189128688913</v>
+        <v>4.088189128688915</v>
       </c>
     </row>
     <row r="31">
@@ -1414,25 +1414,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1742823078008449</v>
+        <v>0.1742823078008453</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1447923902223035</v>
+        <v>0.1447923902223039</v>
       </c>
       <c r="F31" t="n">
-        <v>5.909894706781544</v>
+        <v>5.909894706781558</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>695.2930456525405</v>
+        <v>695.2930456525422</v>
       </c>
       <c r="I31" t="n">
         <v>3989.464303210069</v>
       </c>
       <c r="J31" t="n">
-        <v>3.948111421122615</v>
+        <v>3.948111421122626</v>
       </c>
     </row>
     <row r="32">
@@ -1452,13 +1452,13 @@
         <v>0.1423253379499558</v>
       </c>
       <c r="F32" t="n">
-        <v>5.978298097664378</v>
+        <v>5.97829809766438</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>704.2853859298878</v>
+        <v>704.2853859298879</v>
       </c>
       <c r="I32" t="n">
         <v>4120.688492350118</v>
@@ -1478,25 +1478,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1659421902880722</v>
+        <v>0.1659421902880719</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1381402632976746</v>
+        <v>0.1381402632976741</v>
       </c>
       <c r="F33" t="n">
-        <v>5.968729805865125</v>
+        <v>5.968729805865116</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>704.1443420415306</v>
+        <v>704.1443420415294</v>
       </c>
       <c r="I33" t="n">
         <v>4243.311124308717</v>
       </c>
       <c r="J33" t="n">
-        <v>3.704027719384896</v>
+        <v>3.704027719384889</v>
       </c>
     </row>
     <row r="34">
@@ -1510,25 +1510,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1626770151973614</v>
+        <v>0.1626770151973615</v>
       </c>
       <c r="E34" t="n">
         <v>0.1354912040024705</v>
       </c>
       <c r="F34" t="n">
-        <v>5.983894099431324</v>
+        <v>5.983894099431325</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>703.0416022242491</v>
+        <v>703.0416022242492</v>
       </c>
       <c r="I34" t="n">
         <v>4321.702124736625</v>
       </c>
       <c r="J34" t="n">
-        <v>3.578043486341032</v>
+        <v>3.578043486341034</v>
       </c>
     </row>
     <row r="35">
@@ -1545,22 +1545,22 @@
         <v>0.1694369337011029</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1433185982828985</v>
+        <v>0.1433185982828986</v>
       </c>
       <c r="F35" t="n">
-        <v>6.487279184836808</v>
+        <v>6.487279184836812</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>757.6297216340314</v>
+        <v>757.6297216340317</v>
       </c>
       <c r="I35" t="n">
         <v>4471.455573969113</v>
       </c>
       <c r="J35" t="n">
-        <v>3.784850847895306</v>
+        <v>3.784850847895308</v>
       </c>
     </row>
     <row r="36">
@@ -1577,22 +1577,22 @@
         <v>0.171514080247389</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1462553631817605</v>
+        <v>0.1462553631817606</v>
       </c>
       <c r="F36" t="n">
-        <v>6.79029262657137</v>
+        <v>6.790292626571371</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>783.6740135721458</v>
+        <v>783.6740135721459</v>
       </c>
       <c r="I36" t="n">
         <v>4569.152645903986</v>
       </c>
       <c r="J36" t="n">
-        <v>3.807085593098886</v>
+        <v>3.80708559309889</v>
       </c>
     </row>
     <row r="37">
@@ -1606,25 +1606,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1693885902118238</v>
+        <v>0.1693885902118237</v>
       </c>
       <c r="E37" t="n">
         <v>0.1446680125395566</v>
       </c>
       <c r="F37" t="n">
-        <v>6.852129123254788</v>
+        <v>6.852129123254785</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>789.659765834765</v>
+        <v>789.6597658347648</v>
       </c>
       <c r="I37" t="n">
         <v>4661.82382678361</v>
       </c>
       <c r="J37" t="n">
-        <v>3.760511996712129</v>
+        <v>3.760511996712126</v>
       </c>
     </row>
     <row r="38">
@@ -1641,22 +1641,22 @@
         <v>0.177518171400859</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1537470202852768</v>
+        <v>0.1537470202852769</v>
       </c>
       <c r="F38" t="n">
-        <v>7.467798700101438</v>
+        <v>7.467798700101443</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>849.3642340867136</v>
+        <v>849.364234086714</v>
       </c>
       <c r="I38" t="n">
         <v>4784.660789281901</v>
       </c>
       <c r="J38" t="n">
-        <v>4.007356341706267</v>
+        <v>4.007356341706271</v>
       </c>
     </row>
     <row r="39">
@@ -1670,25 +1670,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1830762476806237</v>
+        <v>0.1830762476806235</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1601289512671581</v>
+        <v>0.160128951267158</v>
       </c>
       <c r="F39" t="n">
-        <v>7.978118397128187</v>
+        <v>7.978118397128177</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>903.0324416441865</v>
+        <v>903.0324416441856</v>
       </c>
       <c r="I39" t="n">
         <v>4932.548340293305</v>
       </c>
       <c r="J39" t="n">
-        <v>4.249461513966827</v>
+        <v>4.24946151396682</v>
       </c>
     </row>
     <row r="40">
@@ -1702,25 +1702,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.178127556986401</v>
+        <v>0.1781275569864013</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1555486437167968</v>
+        <v>0.155548643716797</v>
       </c>
       <c r="F40" t="n">
-        <v>7.889111174637248</v>
+        <v>7.88911117463726</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>903.3243832460298</v>
+        <v>903.3243832460312</v>
       </c>
       <c r="I40" t="n">
         <v>5071.221985686321</v>
       </c>
       <c r="J40" t="n">
-        <v>4.153582946122671</v>
+        <v>4.153582946122677</v>
       </c>
     </row>
     <row r="41">
@@ -1734,25 +1734,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1796612794507078</v>
+        <v>0.1796612794507079</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1577270890616892</v>
+        <v>0.1577270890616894</v>
       </c>
       <c r="F41" t="n">
-        <v>8.190923679620123</v>
+        <v>8.190923679620131</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>929.8807269639422</v>
+        <v>929.8807269639427</v>
       </c>
       <c r="I41" t="n">
         <v>5175.743653874322</v>
       </c>
       <c r="J41" t="n">
-        <v>4.149894283544993</v>
+        <v>4.149894283544994</v>
       </c>
     </row>
     <row r="42">
@@ -1772,19 +1772,19 @@
         <v>0.1581754298587027</v>
       </c>
       <c r="F42" t="n">
-        <v>8.40310054788119</v>
+        <v>8.403100547881191</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>943.4414661298528</v>
+        <v>943.4414661298529</v>
       </c>
       <c r="I42" t="n">
         <v>5254.725389600355</v>
       </c>
       <c r="J42" t="n">
-        <v>4.150818474203917</v>
+        <v>4.150818474203922</v>
       </c>
     </row>
     <row r="43">
@@ -1798,25 +1798,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1812747727109276</v>
+        <v>0.1812747727109282</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1603889250760023</v>
+        <v>0.1603889250760029</v>
       </c>
       <c r="F43" t="n">
-        <v>8.679311267587718</v>
+        <v>8.679311267587746</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>981.2860328532058</v>
+        <v>981.286032853209</v>
       </c>
       <c r="I43" t="n">
         <v>5413.25203820847</v>
       </c>
       <c r="J43" t="n">
-        <v>4.266463213271095</v>
+        <v>4.266463213271111</v>
       </c>
     </row>
     <row r="44">
@@ -1830,25 +1830,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1792090753792349</v>
+        <v>0.1792090753792352</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1587913906871761</v>
+        <v>0.1587913906871763</v>
       </c>
       <c r="F44" t="n">
-        <v>8.777149715165097</v>
+        <v>8.777149715165111</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>987.7082951914917</v>
+        <v>987.7082951914931</v>
       </c>
       <c r="I44" t="n">
         <v>5511.485917224581</v>
       </c>
       <c r="J44" t="n">
-        <v>4.179563987248719</v>
+        <v>4.179563987248722</v>
       </c>
     </row>
     <row r="45">
@@ -1862,25 +1862,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1827729557245516</v>
+        <v>0.1827729557245518</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1629373478537883</v>
+        <v>0.1629373478537886</v>
       </c>
       <c r="F45" t="n">
-        <v>9.214386416357314</v>
+        <v>9.214386416357321</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1038.66548470414</v>
+        <v>1038.665484704141</v>
       </c>
       <c r="I45" t="n">
         <v>5682.818229790315</v>
       </c>
       <c r="J45" t="n">
-        <v>4.284264848007721</v>
+        <v>4.284264848007727</v>
       </c>
     </row>
     <row r="46">
@@ -1894,10 +1894,10 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1864715475029138</v>
+        <v>0.1864715475029139</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1671018224434595</v>
+        <v>0.1671018224434596</v>
       </c>
       <c r="F46" t="n">
         <v>9.62695892329646</v>
@@ -1912,7 +1912,7 @@
         <v>5784.59235442906</v>
       </c>
       <c r="J46" t="n">
-        <v>4.383673373597493</v>
+        <v>4.383673373597494</v>
       </c>
     </row>
     <row r="47">
@@ -1926,25 +1926,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1892552850394252</v>
+        <v>0.1892552850394244</v>
       </c>
       <c r="E47" t="n">
-        <v>0.170400756784528</v>
+        <v>0.1704007567845274</v>
       </c>
       <c r="F47" t="n">
-        <v>10.03765686846447</v>
+        <v>10.03765686846443</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1113.660895912228</v>
+        <v>1113.660895912224</v>
       </c>
       <c r="I47" t="n">
         <v>5884.437497638352</v>
       </c>
       <c r="J47" t="n">
-        <v>4.436159608725049</v>
+        <v>4.436159608725032</v>
       </c>
     </row>
     <row r="48">
@@ -1958,25 +1958,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1827320963727194</v>
+        <v>0.1827320963727195</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1641578258357357</v>
+        <v>0.1641578258357358</v>
       </c>
       <c r="F48" t="n">
-        <v>9.837915088448691</v>
+        <v>9.8379150884487</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1086.777967975352</v>
+        <v>1086.777967975353</v>
       </c>
       <c r="I48" t="n">
         <v>5947.384118872291</v>
       </c>
       <c r="J48" t="n">
-        <v>4.239419664537198</v>
+        <v>4.239419664537203</v>
       </c>
     </row>
     <row r="49">
@@ -1990,25 +1990,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1836871092610972</v>
+        <v>0.1836871092610974</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1654658393785324</v>
+        <v>0.1654658393785327</v>
       </c>
       <c r="F49" t="n">
-        <v>10.080916996727</v>
+        <v>10.08091699672701</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1112.638782561442</v>
+        <v>1112.638782561444</v>
       </c>
       <c r="I49" t="n">
         <v>6057.250217705322</v>
       </c>
       <c r="J49" t="n">
-        <v>4.265071278523673</v>
+        <v>4.265071278523682</v>
       </c>
     </row>
   </sheetData>

--- a/results/ref_threshold_sensitivity/tables/SumRel_threshold_metrics.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_threshold_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,25 +486,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5755852889762161</v>
+        <v>0.6443202593770726</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1511705779524322</v>
+        <v>0.2886405187541452</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356185999273623</v>
+        <v>1.811518019689926</v>
       </c>
       <c r="G2" t="n">
-        <v>0.199</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>190.6934098998242</v>
+        <v>165.1808619198125</v>
       </c>
       <c r="I2" t="n">
-        <v>331.3034810861955</v>
+        <v>256.3645322583974</v>
       </c>
       <c r="J2" t="n">
-        <v>8.294327430324556</v>
+        <v>9.68012474643608</v>
       </c>
     </row>
     <row r="3">
@@ -518,25 +518,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5256219687263333</v>
+        <v>0.4689109939172542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2884329530894999</v>
+        <v>0.2033664908758813</v>
       </c>
       <c r="F3" t="n">
-        <v>2.216046840597066</v>
+        <v>1.765847112429949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005</v>
+        <v>0.075</v>
       </c>
       <c r="H3" t="n">
-        <v>254.084670705896</v>
+        <v>158.6504411884297</v>
       </c>
       <c r="I3" t="n">
-        <v>483.3981184644624</v>
+        <v>338.33807107629</v>
       </c>
       <c r="J3" t="n">
-        <v>10.25014890180994</v>
+        <v>5.58995651403557</v>
       </c>
     </row>
     <row r="4">
@@ -550,25 +550,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4240549598658218</v>
+        <v>0.3666652359844062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2183603026750438</v>
+        <v>0.1404742488359799</v>
       </c>
       <c r="F4" t="n">
-        <v>2.061574985258458</v>
+        <v>1.621042644567446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004</v>
+        <v>0.043</v>
       </c>
       <c r="H4" t="n">
-        <v>262.0799181803198</v>
+        <v>142.1628684792252</v>
       </c>
       <c r="I4" t="n">
-        <v>618.0329037142883</v>
+        <v>387.7184268575468</v>
       </c>
       <c r="J4" t="n">
-        <v>8.532316708043751</v>
+        <v>4.456151476143524</v>
       </c>
     </row>
     <row r="5">
@@ -582,25 +582,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3430968682153296</v>
+        <v>0.2911324999107305</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1702276230088375</v>
+        <v>0.1045884209398702</v>
       </c>
       <c r="F5" t="n">
-        <v>1.98471895799337</v>
+        <v>1.560663310874679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0.077</v>
       </c>
       <c r="H5" t="n">
-        <v>248.3873571825597</v>
+        <v>136.9683826522153</v>
       </c>
       <c r="I5" t="n">
-        <v>723.9569351786397</v>
+        <v>470.4675111648947</v>
       </c>
       <c r="J5" t="n">
-        <v>6.183664494146682</v>
+        <v>3.415751845326127</v>
       </c>
     </row>
     <row r="6">
@@ -614,25 +614,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3405615461937538</v>
+        <v>0.2246349589696992</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2031785349841192</v>
+        <v>0.06310057542171998</v>
       </c>
       <c r="F6" t="n">
-        <v>2.478920378838445</v>
+        <v>1.390632471154215</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001</v>
+        <v>0.104</v>
       </c>
       <c r="H6" t="n">
-        <v>311.3986155603586</v>
+        <v>129.4979637321855</v>
       </c>
       <c r="I6" t="n">
-        <v>914.3681047982918</v>
+        <v>576.4817921757822</v>
       </c>
       <c r="J6" t="n">
-        <v>7.388694435646975</v>
+        <v>2.071876596765784</v>
       </c>
     </row>
     <row r="7">
@@ -646,25 +646,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2817620862995145</v>
+        <v>0.1955137158814499</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1535053159958564</v>
+        <v>0.05185545086028032</v>
       </c>
       <c r="F7" t="n">
-        <v>2.196859359801594</v>
+        <v>1.360963922630131</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001</v>
+        <v>0.103</v>
       </c>
       <c r="H7" t="n">
-        <v>290.3417616227973</v>
+        <v>125.5456396122126</v>
       </c>
       <c r="I7" t="n">
-        <v>1030.450070255948</v>
+        <v>642.132134035739</v>
       </c>
       <c r="J7" t="n">
-        <v>5.828707214872598</v>
+        <v>1.709419770825983</v>
       </c>
     </row>
     <row r="8">
@@ -678,25 +678,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2551292489076619</v>
+        <v>0.2186339985917645</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1422700441967016</v>
+        <v>0.1002452104996076</v>
       </c>
       <c r="F8" t="n">
-        <v>2.260597614178341</v>
+        <v>1.846745811956231</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H8" t="n">
-        <v>296.5920555245094</v>
+        <v>174.173133480673</v>
       </c>
       <c r="I8" t="n">
-        <v>1162.51686858473</v>
+        <v>796.6424920302114</v>
       </c>
       <c r="J8" t="n">
-        <v>5.705509415246414</v>
+        <v>2.129642101991388</v>
       </c>
     </row>
     <row r="9">
@@ -710,25 +710,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2600434908304277</v>
+        <v>0.1985267928438633</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1626807922554839</v>
+        <v>0.09306979190226639</v>
       </c>
       <c r="F9" t="n">
-        <v>2.670873903831481</v>
+        <v>1.882537821778274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H9" t="n">
-        <v>340.5974270481969</v>
+        <v>187.8682664424388</v>
       </c>
       <c r="I9" t="n">
-        <v>1309.77101545794</v>
+        <v>946.3118995237725</v>
       </c>
       <c r="J9" t="n">
-        <v>6.079869406982926</v>
+        <v>1.980510461400006</v>
       </c>
     </row>
     <row r="10">
@@ -742,25 +742,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2958595079622763</v>
+        <v>0.2409467313386454</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2120332589101663</v>
+        <v>0.1505832469741984</v>
       </c>
       <c r="F10" t="n">
-        <v>3.529437512805296</v>
+        <v>2.666417004980438</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>436.2145161079192</v>
+        <v>275.667364815095</v>
       </c>
       <c r="I10" t="n">
-        <v>1474.397490593876</v>
+        <v>1144.100869447573</v>
       </c>
       <c r="J10" t="n">
-        <v>7.515089085891455</v>
+        <v>3.567624563745578</v>
       </c>
     </row>
     <row r="11">
@@ -774,25 +774,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.286061195857017</v>
+        <v>0.2042706702842212</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2101102592460613</v>
+        <v>0.1196186139314788</v>
       </c>
       <c r="F11" t="n">
-        <v>3.766394578151311</v>
+        <v>2.413062116684228</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>448.2318414853746</v>
+        <v>250.1224457054725</v>
       </c>
       <c r="I11" t="n">
-        <v>1566.908927100395</v>
+        <v>1224.465780415041</v>
       </c>
       <c r="J11" t="n">
-        <v>7.188244463959986</v>
+        <v>2.871520683989147</v>
       </c>
     </row>
     <row r="12">
@@ -806,25 +806,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2893160670625263</v>
+        <v>0.1921852214151583</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2209810735108461</v>
+        <v>0.114510723474308</v>
       </c>
       <c r="F12" t="n">
-        <v>4.233790800663843</v>
+        <v>2.474238347333883</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>498.1335897537953</v>
+        <v>253.0112899163396</v>
       </c>
       <c r="I12" t="n">
-        <v>1721.762620415201</v>
+        <v>1316.497116965019</v>
       </c>
       <c r="J12" t="n">
-        <v>7.394514241080915</v>
+        <v>2.556795948137522</v>
       </c>
     </row>
     <row r="13">
@@ -838,25 +838,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2794460989117291</v>
+        <v>0.1777104481883768</v>
       </c>
       <c r="E13" t="n">
-        <v>0.215110929171705</v>
+        <v>0.1042917382051962</v>
       </c>
       <c r="F13" t="n">
-        <v>4.343597755954629</v>
+        <v>2.420506274614307</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>506.888973313834</v>
+        <v>247.1104432080927</v>
       </c>
       <c r="I13" t="n">
-        <v>1813.906063773498</v>
+        <v>1390.52287430028</v>
       </c>
       <c r="J13" t="n">
-        <v>7.070405377868595</v>
+        <v>2.410577506300852</v>
       </c>
     </row>
     <row r="14">
@@ -870,25 +870,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2662099333705263</v>
+        <v>0.1521801414972533</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2060632065976186</v>
+        <v>0.08268671047243781</v>
       </c>
       <c r="F14" t="n">
-        <v>4.426008656724394</v>
+        <v>2.189849303064508</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H14" t="n">
-        <v>520.0013463685008</v>
+        <v>221.5673143028797</v>
       </c>
       <c r="I14" t="n">
-        <v>1953.350649935113</v>
+        <v>1455.954187734008</v>
       </c>
       <c r="J14" t="n">
-        <v>6.638738296098114</v>
+        <v>1.975799641944416</v>
       </c>
     </row>
     <row r="15">
@@ -902,25 +902,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2346826155705918</v>
+        <v>0.1336576952556855</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1767040258410912</v>
+        <v>0.06802570247202533</v>
       </c>
       <c r="F15" t="n">
-        <v>4.047746188127459</v>
+        <v>2.036471689900616</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>486.4548087603538</v>
+        <v>208.0440210742577</v>
       </c>
       <c r="I15" t="n">
-        <v>2072.819955485922</v>
+        <v>1556.54353216455</v>
       </c>
       <c r="J15" t="n">
-        <v>5.839829976999286</v>
+        <v>1.41531315510678</v>
       </c>
     </row>
     <row r="16">
@@ -934,25 +934,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2323611456709234</v>
+        <v>0.1350383082764846</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1775297989331323</v>
+        <v>0.07325533029623343</v>
       </c>
       <c r="F16" t="n">
-        <v>4.237742814928419</v>
+        <v>2.185687914228568</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>496.2224308025017</v>
+        <v>226.4931404417058</v>
       </c>
       <c r="I16" t="n">
-        <v>2135.565433582714</v>
+        <v>1677.251021080416</v>
       </c>
       <c r="J16" t="n">
-        <v>5.669571852455072</v>
+        <v>1.633616555137149</v>
       </c>
     </row>
     <row r="17">
@@ -966,25 +966,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2324913222434055</v>
+        <v>0.1319761409598392</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1813240770596326</v>
+        <v>0.07410788369049515</v>
       </c>
       <c r="F17" t="n">
-        <v>4.543752969470733</v>
+        <v>2.280630991625768</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>525.9191440067971</v>
+        <v>231.5695869645354</v>
       </c>
       <c r="I17" t="n">
-        <v>2262.102253675468</v>
+        <v>1754.632203066181</v>
       </c>
       <c r="J17" t="n">
-        <v>5.725451480651319</v>
+        <v>1.555795937951935</v>
       </c>
     </row>
     <row r="18">
@@ -998,25 +998,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2329768550408528</v>
+        <v>0.1310199780786279</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1850379084809062</v>
+        <v>0.07670872670854212</v>
       </c>
       <c r="F18" t="n">
-        <v>4.859865970344588</v>
+        <v>2.412391075024884</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>545.9729369709584</v>
+        <v>246.7061984752153</v>
       </c>
       <c r="I18" t="n">
-        <v>2343.464276205554</v>
+        <v>1882.966262802774</v>
       </c>
       <c r="J18" t="n">
-        <v>5.564041607145979</v>
+        <v>1.685940351533008</v>
       </c>
     </row>
     <row r="19">
@@ -1030,25 +1030,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2224747594224215</v>
+        <v>0.1369750378595389</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1761934951023275</v>
+        <v>0.08560450439879719</v>
       </c>
       <c r="F19" t="n">
-        <v>4.807015596715873</v>
+        <v>2.666412603330615</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>550.5707756198968</v>
+        <v>274.3252213555073</v>
       </c>
       <c r="I19" t="n">
-        <v>2474.756134355478</v>
+        <v>2002.738788339042</v>
       </c>
       <c r="J19" t="n">
-        <v>5.24615075865755</v>
+        <v>1.891149717524331</v>
       </c>
     </row>
     <row r="20">
@@ -1062,25 +1062,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2279835395489326</v>
+        <v>0.1466880592492044</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1846118282876367</v>
+        <v>0.09874918617331707</v>
       </c>
       <c r="F20" t="n">
-        <v>5.256503211861522</v>
+        <v>3.059897945806875</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>591.9513970181738</v>
+        <v>323.223850557419</v>
       </c>
       <c r="I20" t="n">
-        <v>2596.465508822938</v>
+        <v>2203.477585099839</v>
       </c>
       <c r="J20" t="n">
-        <v>5.353943655071093</v>
+        <v>2.185895472559385</v>
       </c>
     </row>
     <row r="21">
@@ -1094,25 +1094,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2141315808957047</v>
+        <v>0.1567278246711239</v>
       </c>
       <c r="E21" t="n">
-        <v>0.172330069241221</v>
+        <v>0.1118729217280986</v>
       </c>
       <c r="F21" t="n">
-        <v>5.1225798403091</v>
+        <v>3.494106873226311</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>584.9491316892047</v>
+        <v>380.413557026489</v>
       </c>
       <c r="I21" t="n">
-        <v>2731.727516522241</v>
+        <v>2427.224124527633</v>
       </c>
       <c r="J21" t="n">
-        <v>4.985494666598618</v>
+        <v>2.727766722989574</v>
       </c>
     </row>
     <row r="22">
@@ -1126,25 +1126,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2232963412792219</v>
+        <v>0.1676838342009694</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1836686035893864</v>
+        <v>0.1252187237010189</v>
       </c>
       <c r="F22" t="n">
-        <v>5.634849585079812</v>
+        <v>3.948743620981858</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>635.678056637066</v>
+        <v>427.3427058190591</v>
       </c>
       <c r="I22" t="n">
-        <v>2846.791187868947</v>
+        <v>2548.502709610564</v>
       </c>
       <c r="J22" t="n">
-        <v>5.342279290739274</v>
+        <v>3.142273567068756</v>
       </c>
     </row>
     <row r="23">
@@ -1158,25 +1158,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2185174809382151</v>
+        <v>0.1553402395353086</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1805814363235654</v>
+        <v>0.114337338541877</v>
       </c>
       <c r="F23" t="n">
-        <v>5.760154574834885</v>
+        <v>3.788518269968095</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>655.3893111570943</v>
+        <v>413.7535447079672</v>
       </c>
       <c r="I23" t="n">
-        <v>2999.253461751203</v>
+        <v>2663.531007456194</v>
       </c>
       <c r="J23" t="n">
-        <v>5.299448413396805</v>
+        <v>2.882354577134603</v>
       </c>
     </row>
     <row r="24">
@@ -1190,25 +1190,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.220858236645828</v>
+        <v>0.1541046092455618</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1847868587127646</v>
+        <v>0.114942785599523</v>
       </c>
       <c r="F24" t="n">
-        <v>6.122811195504295</v>
+        <v>3.935072345926091</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>705.6293275768203</v>
+        <v>422.8410738954885</v>
       </c>
       <c r="I24" t="n">
-        <v>3194.942322700781</v>
+        <v>2743.857409363415</v>
       </c>
       <c r="J24" t="n">
-        <v>5.398015944144066</v>
+        <v>2.846123390401187</v>
       </c>
     </row>
     <row r="25">
@@ -1222,25 +1222,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2061241458806003</v>
+        <v>0.1522261841554092</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1706832595359842</v>
+        <v>0.1143791388052041</v>
       </c>
       <c r="F25" t="n">
-        <v>5.815998614603307</v>
+        <v>4.022141827633709</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>678.8132858778257</v>
+        <v>434.1694188203772</v>
       </c>
       <c r="I25" t="n">
-        <v>3293.225463605006</v>
+        <v>2852.133627531053</v>
       </c>
       <c r="J25" t="n">
-        <v>4.960461723362688</v>
+        <v>2.907770016140893</v>
       </c>
     </row>
     <row r="26">
@@ -1254,25 +1254,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2031645653783599</v>
+        <v>0.1547169841265005</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1691117690270078</v>
+        <v>0.1185937783199408</v>
       </c>
       <c r="F26" t="n">
-        <v>5.966163932093431</v>
+        <v>4.283035812353194</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>689.9503162673107</v>
+        <v>471.4786403214896</v>
       </c>
       <c r="I26" t="n">
-        <v>3396.016992345067</v>
+        <v>3047.361884562051</v>
       </c>
       <c r="J26" t="n">
-        <v>4.853376658121173</v>
+        <v>3.028543115037929</v>
       </c>
     </row>
     <row r="27">
@@ -1286,25 +1286,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1918685918658001</v>
+        <v>0.1493817852781252</v>
       </c>
       <c r="E27" t="n">
-        <v>0.158748452188169</v>
+        <v>0.1145203830354254</v>
       </c>
       <c r="F27" t="n">
-        <v>5.793109380978406</v>
+        <v>4.285019410239204</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>676.0836276193372</v>
+        <v>471.694216216854</v>
       </c>
       <c r="I27" t="n">
-        <v>3523.680562018274</v>
+        <v>3157.642113719784</v>
       </c>
       <c r="J27" t="n">
-        <v>4.492789531176012</v>
+        <v>2.930842958724122</v>
       </c>
     </row>
     <row r="28">
@@ -1318,25 +1318,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1912461827455567</v>
+        <v>0.1484273234033903</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1591527772989517</v>
+        <v>0.1146347568717788</v>
       </c>
       <c r="F28" t="n">
-        <v>5.959049221614723</v>
+        <v>4.392306907631384</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>697.0485726523991</v>
+        <v>482.9139844610169</v>
       </c>
       <c r="I28" t="n">
-        <v>3644.77116690892</v>
+        <v>3253.538320222693</v>
       </c>
       <c r="J28" t="n">
-        <v>4.51205329740503</v>
+        <v>2.904762257520165</v>
       </c>
     </row>
     <row r="29">
@@ -1350,25 +1350,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1837642497820643</v>
+        <v>0.1376309138251438</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1526102135142043</v>
+        <v>0.1047160632077828</v>
       </c>
       <c r="F29" t="n">
-        <v>5.898569552980956</v>
+        <v>4.181423012521599</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>692.1452534146139</v>
+        <v>465.1358431524944</v>
       </c>
       <c r="I29" t="n">
-        <v>3766.484799058931</v>
+        <v>3379.588424032675</v>
       </c>
       <c r="J29" t="n">
-        <v>4.283247081278818</v>
+        <v>2.61336349566819</v>
       </c>
     </row>
     <row r="30">
@@ -1382,25 +1382,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1788636025916064</v>
+        <v>0.1417671268639166</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1486747644515919</v>
+        <v>0.1102144477045017</v>
       </c>
       <c r="F30" t="n">
-        <v>5.924825651190848</v>
+        <v>4.493029772453269</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>690.6982062168773</v>
+        <v>498.0211495626916</v>
       </c>
       <c r="I30" t="n">
-        <v>3861.591716867779</v>
+        <v>3512.952266012599</v>
       </c>
       <c r="J30" t="n">
-        <v>4.088189128688915</v>
+        <v>2.781984303448982</v>
       </c>
     </row>
     <row r="31">
@@ -1414,25 +1414,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1742823078008453</v>
+        <v>0.1394167525559828</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1447923902223039</v>
+        <v>0.1086816365758393</v>
       </c>
       <c r="F31" t="n">
-        <v>5.909894706781558</v>
+        <v>4.53607374203675</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>695.2930456525422</v>
+        <v>499.6936543517871</v>
       </c>
       <c r="I31" t="n">
-        <v>3989.464303210069</v>
+        <v>3584.172240356373</v>
       </c>
       <c r="J31" t="n">
-        <v>3.948111421122626</v>
+        <v>2.715299503723694</v>
       </c>
     </row>
     <row r="32">
@@ -1446,25 +1446,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.170914493351624</v>
+        <v>0.1364507801322241</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1423253379499558</v>
+        <v>0.1066732208264387</v>
       </c>
       <c r="F32" t="n">
-        <v>5.97829809766438</v>
+        <v>4.58233593730812</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>704.2853859298879</v>
+        <v>508.4682413583382</v>
       </c>
       <c r="I32" t="n">
-        <v>4120.688492350118</v>
+        <v>3726.385740452491</v>
       </c>
       <c r="J32" t="n">
-        <v>3.857194469720433</v>
+        <v>2.671107622734316</v>
       </c>
     </row>
     <row r="33">
@@ -1478,25 +1478,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1659421902880719</v>
+        <v>0.1370440693141079</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1381402632976741</v>
+        <v>0.1082788716245781</v>
       </c>
       <c r="F33" t="n">
-        <v>5.968729805865116</v>
+        <v>4.76423179125206</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>704.1443420415294</v>
+        <v>521.0601225137525</v>
       </c>
       <c r="I33" t="n">
-        <v>4243.311124308717</v>
+        <v>3802.135511019246</v>
       </c>
       <c r="J33" t="n">
-        <v>3.704027719384889</v>
+        <v>2.672412769473156</v>
       </c>
     </row>
     <row r="34">
@@ -1510,25 +1510,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1626770151973615</v>
+        <v>0.138609563908845</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1354912040024705</v>
+        <v>0.1106423419578334</v>
       </c>
       <c r="F34" t="n">
-        <v>5.983894099431325</v>
+        <v>4.956143450773869</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>703.0416022242492</v>
+        <v>549.6988678489253</v>
       </c>
       <c r="I34" t="n">
-        <v>4321.702124736625</v>
+        <v>3965.807642324224</v>
       </c>
       <c r="J34" t="n">
-        <v>3.578043486341034</v>
+        <v>2.775446544737478</v>
       </c>
     </row>
     <row r="35">
@@ -1542,25 +1542,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1694369337011029</v>
+        <v>0.1523016141160933</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1433185982828986</v>
+        <v>0.1256444321700585</v>
       </c>
       <c r="F35" t="n">
-        <v>6.487279184836812</v>
+        <v>5.713342634056928</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>757.6297216340317</v>
+        <v>639.1000296499849</v>
       </c>
       <c r="I35" t="n">
-        <v>4471.455573969113</v>
+        <v>4196.278768016373</v>
       </c>
       <c r="J35" t="n">
-        <v>3.784850847895308</v>
+        <v>3.237921027698854</v>
       </c>
     </row>
     <row r="36">
@@ -1574,25 +1574,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.171514080247389</v>
+        <v>0.1805324117799927</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1462553631817606</v>
+        <v>0.1555486438464558</v>
       </c>
       <c r="F36" t="n">
-        <v>6.790292626571371</v>
+        <v>7.22598818001572</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>783.6740135721459</v>
+        <v>805.5186080965218</v>
       </c>
       <c r="I36" t="n">
-        <v>4569.152645903986</v>
+        <v>4461.905760602</v>
       </c>
       <c r="J36" t="n">
-        <v>3.80708559309889</v>
+        <v>4.126753107596748</v>
       </c>
     </row>
     <row r="37">
@@ -1606,25 +1606,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1693885902118237</v>
+        <v>0.1774486907954965</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1446680125395566</v>
+        <v>0.152967997069172</v>
       </c>
       <c r="F37" t="n">
-        <v>6.852129123254785</v>
+        <v>7.248515617214017</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>789.6597658347648</v>
+        <v>812.6671136644674</v>
       </c>
       <c r="I37" t="n">
-        <v>4661.82382678361</v>
+        <v>4579.730118161528</v>
       </c>
       <c r="J37" t="n">
-        <v>3.760511996712126</v>
+        <v>4.076469854159391</v>
       </c>
     </row>
     <row r="38">
@@ -1638,25 +1638,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.177518171400859</v>
+        <v>0.1866865354610838</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1537470202852769</v>
+        <v>0.1631803659657394</v>
       </c>
       <c r="F38" t="n">
-        <v>7.467798700101443</v>
+        <v>7.94202285906509</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>849.364234086714</v>
+        <v>888.8960647038859</v>
       </c>
       <c r="I38" t="n">
-        <v>4784.660789281901</v>
+        <v>4761.436396623168</v>
       </c>
       <c r="J38" t="n">
-        <v>4.007356341706271</v>
+        <v>4.366638798108564</v>
       </c>
     </row>
     <row r="39">
@@ -1670,25 +1670,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1830762476806235</v>
+        <v>0.1814949099839207</v>
       </c>
       <c r="E39" t="n">
-        <v>0.160128951267158</v>
+        <v>0.1585031939722331</v>
       </c>
       <c r="F39" t="n">
-        <v>7.978118397128177</v>
+        <v>7.893926225065565</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>903.0324416441856</v>
+        <v>880.9954548466064</v>
       </c>
       <c r="I39" t="n">
-        <v>4932.548340293305</v>
+        <v>4854.105577531937</v>
       </c>
       <c r="J39" t="n">
-        <v>4.24946151396682</v>
+        <v>4.205615155331319</v>
       </c>
     </row>
     <row r="40">
@@ -1702,25 +1702,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1781275569864013</v>
+        <v>0.1888261267831572</v>
       </c>
       <c r="E40" t="n">
-        <v>0.155548643716797</v>
+        <v>0.1665411302662111</v>
       </c>
       <c r="F40" t="n">
-        <v>7.88911117463726</v>
+        <v>8.473240129948765</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>903.3243832460312</v>
+        <v>937.9072095158523</v>
       </c>
       <c r="I40" t="n">
-        <v>5071.221985686321</v>
+        <v>4967.041507941956</v>
       </c>
       <c r="J40" t="n">
-        <v>4.153582946122677</v>
+        <v>4.429145188090675</v>
       </c>
     </row>
     <row r="41">
@@ -1734,25 +1734,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1796612794507079</v>
+        <v>0.1928483851718919</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1577270890616894</v>
+        <v>0.1712667911925306</v>
       </c>
       <c r="F41" t="n">
-        <v>8.190923679620131</v>
+        <v>8.935780431988279</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>929.8807269639427</v>
+        <v>986.363792289834</v>
       </c>
       <c r="I41" t="n">
-        <v>5175.743653874322</v>
+        <v>5114.711183143467</v>
       </c>
       <c r="J41" t="n">
-        <v>4.149894283544994</v>
+        <v>4.542367873475873</v>
       </c>
     </row>
     <row r="42">
@@ -1766,25 +1766,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1795415356998524</v>
+        <v>0.188363479786846</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1581754298587027</v>
+        <v>0.1672271120729618</v>
       </c>
       <c r="F42" t="n">
-        <v>8.403100547881191</v>
+        <v>8.911818829831976</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>943.4414661298529</v>
+        <v>988.2981664583608</v>
       </c>
       <c r="I42" t="n">
-        <v>5254.725389600355</v>
+        <v>5246.76103656998</v>
       </c>
       <c r="J42" t="n">
-        <v>4.150818474203922</v>
+        <v>4.396786209411307</v>
       </c>
     </row>
     <row r="43">
@@ -1798,25 +1798,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1812747727109282</v>
+        <v>0.187844403013537</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1603889250760029</v>
+        <v>0.1671261479883721</v>
       </c>
       <c r="F43" t="n">
-        <v>8.679311267587746</v>
+        <v>9.066613128633509</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>981.286032853209</v>
+        <v>999.8139063199339</v>
       </c>
       <c r="I43" t="n">
-        <v>5413.25203820847</v>
+        <v>5322.564262124342</v>
       </c>
       <c r="J43" t="n">
-        <v>4.266463213271111</v>
+        <v>4.361917920560377</v>
       </c>
     </row>
     <row r="44">
@@ -1830,25 +1830,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1792090753792352</v>
+        <v>0.1888711837942516</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1587913906871763</v>
+        <v>0.1686938500577903</v>
       </c>
       <c r="F44" t="n">
-        <v>8.777149715165111</v>
+        <v>9.360562017812709</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>987.7082951914931</v>
+        <v>1028.572489820757</v>
       </c>
       <c r="I44" t="n">
-        <v>5511.485917224581</v>
+        <v>5445.894228847746</v>
       </c>
       <c r="J44" t="n">
-        <v>4.179563987248722</v>
+        <v>4.389608069601873</v>
       </c>
     </row>
     <row r="45">
@@ -1862,25 +1862,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1827729557245518</v>
+        <v>0.1943698516063707</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1629373478537886</v>
+        <v>0.1748157217909915</v>
       </c>
       <c r="F45" t="n">
-        <v>9.214386416357321</v>
+        <v>9.940092115656233</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1038.665484704141</v>
+        <v>1098.768322025674</v>
       </c>
       <c r="I45" t="n">
-        <v>5682.818229790315</v>
+        <v>5652.977110106825</v>
       </c>
       <c r="J45" t="n">
-        <v>4.284264848007727</v>
+        <v>4.623652537044055</v>
       </c>
     </row>
     <row r="46">
@@ -1894,25 +1894,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1864715475029139</v>
+        <v>0.1965238362362337</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1671018224434596</v>
+        <v>0.1773934513847154</v>
       </c>
       <c r="F46" t="n">
-        <v>9.62695892329646</v>
+        <v>10.27286370669313</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1078.661888003911</v>
+        <v>1126.205494710873</v>
       </c>
       <c r="I46" t="n">
-        <v>5784.59235442906</v>
+        <v>5730.630524416922</v>
       </c>
       <c r="J46" t="n">
-        <v>4.383673373597494</v>
+        <v>4.656005089795618</v>
       </c>
     </row>
     <row r="47">
@@ -1926,25 +1926,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1892552850394244</v>
+        <v>0.1949041271119488</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1704007567845274</v>
+        <v>0.1761809672773428</v>
       </c>
       <c r="F47" t="n">
-        <v>10.03765686846443</v>
+        <v>10.40978813585243</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1113.660895912224</v>
+        <v>1143.521701290344</v>
       </c>
       <c r="I47" t="n">
-        <v>5884.437497638352</v>
+        <v>5867.098445963282</v>
       </c>
       <c r="J47" t="n">
-        <v>4.436159608725032</v>
+        <v>4.560324768272891</v>
       </c>
     </row>
     <row r="48">
@@ -1958,25 +1958,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1827320963727195</v>
+        <v>0.1938227571238266</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1641578258357358</v>
+        <v>0.1755005470584591</v>
       </c>
       <c r="F48" t="n">
-        <v>9.8379150884487</v>
+        <v>10.57856865696503</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1086.777967975353</v>
+        <v>1153.967281963643</v>
       </c>
       <c r="I48" t="n">
-        <v>5947.384118872291</v>
+        <v>5953.724418574922</v>
       </c>
       <c r="J48" t="n">
-        <v>4.239419664537203</v>
+        <v>4.51404346325082</v>
       </c>
     </row>
     <row r="49">
@@ -1990,25 +1990,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1836871092610974</v>
+        <v>0.1864351717766692</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1654658393785327</v>
+        <v>0.1682752425752556</v>
       </c>
       <c r="F49" t="n">
-        <v>10.08091699672701</v>
+        <v>10.26629397663932</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1112.638782561444</v>
+        <v>1129.748906081588</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.250217705322</v>
+        <v>6059.741277975782</v>
       </c>
       <c r="J49" t="n">
-        <v>4.265071278523682</v>
+        <v>4.346852164633938</v>
       </c>
     </row>
   </sheetData>
